--- a/artfynd/A 55646-2023 artfynd.xlsx
+++ b/artfynd/A 55646-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55646-2023 artfynd.xlsx
+++ b/artfynd/A 55646-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103986828</v>
+        <v>103986820</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550610.8164113951</v>
+        <v>550693</v>
       </c>
       <c r="R2" t="n">
-        <v>7027105.513367397</v>
+        <v>7027131</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>104044310</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550738.8880599341</v>
+        <v>550739</v>
       </c>
       <c r="R3" t="n">
-        <v>7027331.895034114</v>
+        <v>7027332</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104044311</v>
+        <v>104044309</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550641.0642034446</v>
+        <v>550735</v>
       </c>
       <c r="R4" t="n">
-        <v>7027181.825437536</v>
+        <v>7027346</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104044309</v>
+        <v>103986823</v>
       </c>
       <c r="B5" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1352</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rävatjärnbrännan, Jmt</t>
+          <t>Köttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550735.0672701332</v>
+        <v>550768</v>
       </c>
       <c r="R5" t="n">
-        <v>7027346.192846178</v>
+        <v>7027378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104044313</v>
+        <v>104044312</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550611.1864822585</v>
+        <v>550630</v>
       </c>
       <c r="R6" t="n">
-        <v>7027167.443196672</v>
+        <v>7027221</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104044308</v>
+        <v>104044313</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550808.2557594482</v>
+        <v>550611</v>
       </c>
       <c r="R7" t="n">
-        <v>7027320.879141223</v>
+        <v>7027168</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104044312</v>
+        <v>104044311</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550630.5649482826</v>
+        <v>550641</v>
       </c>
       <c r="R8" t="n">
-        <v>7027220.697818358</v>
+        <v>7027182</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2022-10-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104044314</v>
+        <v>103986828</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rävatjärnbrännan, Jmt</t>
+          <t>Köttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550808.4477755176</v>
+        <v>550611</v>
       </c>
       <c r="R9" t="n">
-        <v>7027308.767268367</v>
+        <v>7027105</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,15 +1439,209 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104044314</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rävatjärnbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>550808</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7027309</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104044308</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rävatjärnbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>550808</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7027321</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55646-2023 artfynd.xlsx
+++ b/artfynd/A 55646-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986820</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044310</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044309</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986823</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044312</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044313</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044311</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986828</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044314</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,8 +1692,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044308</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>